--- a/Company_email.xlsx
+++ b/Company_email.xlsx
@@ -1,75 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nehal\Project\automation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7875"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Comapany Name</t>
-  </si>
-  <si>
-    <t>EmailID</t>
-  </si>
-  <si>
-    <t>Website</t>
-  </si>
-  <si>
-    <t>Job Title</t>
-  </si>
-  <si>
-    <t>Role Searched</t>
-  </si>
-  <si>
-    <t>Experience</t>
-  </si>
-  <si>
-    <t>Job URL</t>
-  </si>
-  <si>
-    <t>Career Page</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -88,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -390,48 +408,2701 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="56.5703125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B321"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Email ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TechGropse Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>info@techgropse.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rishabh Software Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rise@rishabhsoft.com, contact@dailyremote.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vinsys IT Corporate Training Company in India</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>enquiry@vinsys.com, hi@tracxn.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dean Infotech™</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>editor@mobileappdaily.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SynergyTop</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>contact@synergytop.com, careers@synergytop.com, hr@synergytop.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Prometteur Solutions PVT LTD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hr@prometteursolutions.com, career@prometteursolutions.com, abc@xyz.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>iProgrammer Solutions Private Limited</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>editor@mobileappdaily.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>info@magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vibeosys Software Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NO email id</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Futurism AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>info@crmxchange.com, emarketing@futurismai.com, info@c2creview.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Eternalight Infotech</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>info@eternalight.in, contact@eternalight.in, name@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Webkorps Services</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>info@selectedfirms.co, name@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Teqrox Solution LLP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hello@aipeakflow.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Futurism Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NO email id</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Awrange</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>careers@awrange.com, contact@exploresys.com, contact@digitizebrand.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Interpretors</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>recruitment9@intalent.asia, Jessica.thompson@pathyorkshire.co.uk, vamsikrishna.r@websynergies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bellbird Cybersecurity Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>you@company.com, careers@india.sun.com, careers@wipro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Graphinet Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NO email id</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Doodlo design Studio</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>contact@doodlodesigns.com, info@selectedfirms.co, info@c2creview.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DataIntelo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>info+jobs@canarymail.io, hello@canarymail.io, dd_hr@datadynamicsinc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kreeda Labs</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>careers@kreedalabs.com, info@kreedalabs.com, veena.yadav@rfhospital.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Teleglobal International Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>hello@teleglobals.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>jobs@persistentsystems.com, feedback@forbes.com, corrections@forbes.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Setoo Solutions</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NO email id</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Intelisync Technology Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>careers@india.sun.com, careers@wipro.com, careers@bhartitelesoft.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DWT Technology Services</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>info@dwttechnology.com, applicant.accomodations@ltts.com, info@ltts.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FORESIENCE SYSTEMS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>contact@foresience.com, name@company.com, talent@magnetforensics.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mechsoft Digital Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>hr@mechsoftgroup.com, contactus@mechsoftgroup.com, pxxx@mechsoftgroup.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Imperium Digital Network Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NO email id</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Microscan Communications</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Techcraftery</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Explicate Technologies Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Staqwise Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Andro Buddy Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nimap Infotech</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dimentrix Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tech9</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SynGrow Consulting Services Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Poscig Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HoriZayn Digital</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Icreon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Netfotech Solutions</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NumeroEins</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>[6:22 PM]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TechGropse Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Haraay Design Studio</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Vinsys IT Corporate Training Company in India</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dean Infotech™</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SynergyTop</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Prometteur Solutions PVT LTD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>iProgrammer Solutions Private Limited</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jayshinde.com</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Andro Buddy Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Futurism AI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Eternalight Infotech</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Futurism Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Vibeosys Software Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Eilan Digital Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Teqrox Solution LLP</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Webkorps Services</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guruteck</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Infysion Technologies</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Growg Web Services</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Kodesoft Technologies</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ITvia Data Solutions</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Graphinet Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Awrange</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>[6:23 PM]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TechGropse Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Rishabh Software Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Volar Media House</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Futurism AI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Eternalight Infotech</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Futurism Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Bellbird Cybersecurity Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DWT Technology Services</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SynGrow Consulting Services Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Bharat Tech Bundle</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Poscig Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Techcraftery</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Vsynergize.AI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Praxis Info Solutions</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>XSAV Technology Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Moxart</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sagacity Softwares Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mckinley &amp; Rice Inc.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Quadrect Infotech LLP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Netfotech Solutions</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NEXTIN CUBE SOLUTION LLP</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Infysion Technologies</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ubmatic</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EWEBAC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>[6:23 PM]</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>iProgrammer Solutions Private Limited</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Jayshinde.com</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Kodesoft Technologies</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Compumatrix Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Vibeosys Software Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Prometteur Solutions PVT LTD</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Vinsys IT Corporate Training Company in India</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SimpliSage Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TechGropse Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Andro Buddy Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Eternalight Infotech</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Uinest</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EfficiaLabs</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Loud Mob Media</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Praxis Info Solutions</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Mckinley &amp; Rice Inc.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Quadrect Infotech LLP</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Bharat Tech Bundle</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>XSAV Technology Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Vsynergize.AI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Moxart</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sagacity Softwares Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>NEXTIN CUBE SOLUTION LLP</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ubmatic</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>EWEBAC</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TechGropse Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Vinsys IT Corporate Training Company in India</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SynergyTop</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Dean Infotech™</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Rishabh Software Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Prometteur Solutions PVT LTD</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>iProgrammer Solutions Private Limited</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Awrange</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Fifth Estate</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FORESIENCE SYSTEMS</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Feligrat Global Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Cogniwize Infosystem Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Bellbird Cybersecurity Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Bharat Tech Bundle</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Poscig Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Techcraftery</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Eilan Digital Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>THE VANILLA THEORY</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Brain Behind Brands</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Reality Premedia Services</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Webducts</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FDA Solutions</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SRV Media</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Atellier Studio</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Unplug Infinity Media Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>XSAV Technology Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Ancrew Global Services</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Compumatrix Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SimpliSage Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Interpretors</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Doodlo Design Studio</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Kreeda Labs</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DataIntelo</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Teleglobal International Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Intelisync Technology Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mechsoft Digital Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Imperium Digital Network Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Microscan Communications</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Explicate Technologies Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Staqwise Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Nimap Infotech</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Dimentrix Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tech9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>HoriZayn Digital</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Page 6</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Icreon</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>NumeroEins</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Setoo Solutions</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Netfotech Solutions</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Webkorps Services</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Teqrox Solution LLP</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Graphinet Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Bellbird Cybersecurity Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Futurism AI</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Eternalight Infotech</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Page 7</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Ajackus</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>CodePlateau Technology</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mindbowser InfoSolutions</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Salt Technologies</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Panorbit Services LLP</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Thinkitive Technologies Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Brainmine Web Solutions</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Optimind Technology Solutions</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ambit Software Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Innowrap Technologies</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Page 8</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Helios Solutions</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Velotio Technologies</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Sphinx Solutions</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Harbinger Systems</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Codiastic Softwares Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Cuelogic Technologies</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Cynoteck Technology Solutions</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Yashus Digital Marketing</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>IKF</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Digital Tokri</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Page 9</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Mobisoft Infotech</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PiTech India</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Pratiti Technologies</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>NS Websolution Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Brainmine Tech</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Softenger</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Exioms Technology</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Tactable</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Kanhasoft</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Probytes</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Page 10</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Rego Techno Solutions</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Evon Technologies</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Right Symbol</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Lead Million</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Webtech Developers</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Tavisca Solutions</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>WPoets Technology LLP</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Accrevent</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Amura Marketing Technologies</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Hexanovate</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>XDBS Worldwide</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Shrofile</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Public Media Solution</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ProAzure Software Solutions</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>3RI Technologies</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Leo9 Studio</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>OM Software Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Digital Flame</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>A2 Consulting</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Panacea Infotech</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Page 12</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Saviant Consulting</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Corigami Technologies</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Techspawn Solutions</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Mediapro Education Technology</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Webwingz Technologies</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>A2Z IT Hub</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Osumare Marketing Solutions</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Saletify</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Web Techneeq</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Tectigon IT Solutions</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Page 13</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CloudTrains Technologies</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Verve Systems Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Capermint Technologies</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Bright Pixel Infotech</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Techila Global Services</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>PiServe Solutions</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Mplussoft Technologies</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Ideamagix</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SIB Infotech</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Kyliv Technologies</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Page 14</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Biz4Group LLC</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>eLuminous Technologies</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>AddWeb Solution</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Aress Software</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>TechVerito</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Webomindapps</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Cybage Software</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Aloha Technology</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SpryBit Softlabs</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Netwin Infosolutions</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Page 15</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Anuyat</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Excellon Software</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Smart Sight Innovations</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TechUp Labs</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Panaceatek</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Mindstorm</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Aarav Infotech</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>iKnowledge Factory</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Seagull Advertising</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>NGenious Solutions</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Page 16</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Webxion Technologies</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Nirmitee.io</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Decos Software Development</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Softlink Global</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Bitwise Solutions</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Aexonic Technologies</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Binary Republik</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Appzia Technologies</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SkyHigh Technologies</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Trinesis</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Page 17</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Webguruz Technologies</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Logicwind</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>C-Metric Solutions</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Virtuoso Infotech</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Avisys Services</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Kreeti Technologies</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>AQe Digital</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>7k Network</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Metizsoft Solutions</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Pace Wisdom Solutions</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Page 18</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Rudra Innovative Software</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Maven Cluster</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Codevian Technologies</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Tudip Technologies</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SR Analytics</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Xoriant Solutions</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SynapseIndia</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Innvonix Technologies</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Thinkitive Lab</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Page 19</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Webners Solutions</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Digifine Solutions</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Openxcell</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Pixel Values Technolabs</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Innoraft Solutions</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>MavenBird Technologies</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Cogent Web Services</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Webs Optimization</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Smartinfosys.net</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CMARIX TechnoLabs</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Company_email.xlsx
+++ b/Company_email.xlsx
@@ -782,7 +782,11 @@
           <t>Microscan Communications</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>info.communication@microscan.co.in</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -790,7 +794,11 @@
           <t>Techcraftery</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Contact@vision-services.co.in, sample@mail.com</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -798,7 +806,11 @@
           <t>Explicate Technologies Pvt. Ltd</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>contact@explicate.in, explicate22@gmail.com.Explicate, info@welistthem.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -806,7 +818,11 @@
           <t>Staqwise Solutions Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>info@staqwise.com</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -814,7 +830,11 @@
           <t>Andro Buddy Technologies Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>hello@androtechbuddy.com, info@jobringer.com</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -822,7 +842,11 @@
           <t>Nimap Infotech</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>google@2x-1-qrp1052lld4k7ztnoysaci57tc63qfas3ubcbzka9s.png, akansha.chauhan@avotima.com</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -830,7 +854,11 @@
           <t>Dimentrix Technologies Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>info@pdfcoffee.com, careers-hero-bg@2x.jpg, careers-hero-bg@2x-300x125.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -838,7 +866,11 @@
           <t>Tech9</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hr@a9kh.com, careers@monadel.com.au, monadel@monadel.com.au</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -846,7 +878,11 @@
           <t>SynGrow Consulting Services Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>contact@syngrowconsulting.com, SynGrowConsultingServices@syngrowconsulting.in, hr@syngrowconsulting.com</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -854,7 +890,11 @@
           <t>Poscig Technologies Pvt Ltd</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NO email id</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -862,7 +902,11 @@
           <t>HoriZayn Digital</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>admin@weboworld.com, jobs@hil.us, internships@horizon.com</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -870,7 +914,11 @@
           <t>Icreon</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>team@levels.fyi, jdoe@icreon.com, jane.doe@icreon.com</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -878,7 +926,11 @@
           <t>Netfotech Solutions</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>hr@netsolutions.com</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -886,7 +938,11 @@
           <t>NumeroEins</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>info@ggcity.org</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -894,7 +950,11 @@
           <t>[6:22 PM]</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>paige.mcglauflin@fortune.com, corporate.careers@walgreens.com, yourhrsupport@hr.wba.com</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -902,7 +962,11 @@
           <t>TechGropse Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>info@techgropse.com, Hr@techgropse.com, roshnisarin@techgropse.com</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -910,7 +974,11 @@
           <t>Haraay Design Studio</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ashish@innovativezoneglobal.com, techblog-logo-dark@2x.png</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -918,7 +986,11 @@
           <t>Vinsys IT Corporate Training Company in India</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>enquiry@vinsys.com, hi@tracxn.com</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -926,7 +998,11 @@
           <t>Dean Infotech™</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>editor@mobileappdaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -934,7 +1010,11 @@
           <t>SynergyTop</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hr@synergytop.com, name@company.com, hello@puzzly.com</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -942,7 +1022,11 @@
           <t>Prometteur Solutions PVT LTD</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hr@prometteursolutions.com, career@prometteursolutions.com, abc@xyz.com</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -950,7 +1034,11 @@
           <t>iProgrammer Solutions Private Limited</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>info@lobitech.com, veena.yadav@rfhospital.org, Careers@isolvedhcm.com</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -958,7 +1046,11 @@
           <t>Magneto IT Solutions</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>info@magnetoitsolutions.com, name@company.com, sxxx@magnetoitsolutions.com</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
